--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-18T20:00:37+00:00</t>
+    <t>2022-02-19T15:25:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-19T15:25:03+00:00</t>
+    <t>2022-05-23T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-23T06:59:28+00:00</t>
+    <t>2022-05-24T18:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-24T18:54:59+00:00</t>
+    <t>2022-08-17T21:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1199,44 +1199,44 @@
   <dimension ref="A1:AM35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.70703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="25.4140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.7734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.2734375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.2578125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.44140625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="14.4453125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="83.33984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.265625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="15.26953125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="17.16796875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="19.03125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="18.85546875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="58.06640625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="60.06640625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="60.0703125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="23.2734375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="80.66015625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.2109375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="80.6640625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="10.55078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="13.87109375" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="11.0390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="13.875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="36" max="36" width="62.87890625" customWidth="true" bestFit="true"/>
     <col min="37" max="37" width="143.74609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="52.37890625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="52.3828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-17T21:15:17+00:00</t>
+    <t>2022-09-06T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T15:19:36+00:00</t>
+    <t>2022-09-06T18:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T18:47:55+00:00</t>
+    <t>2022-09-06T19:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:01:15+00:00</t>
+    <t>2022-09-06T19:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:02:52+00:00</t>
+    <t>2022-09-06T19:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="281">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:21:39+00:00</t>
+    <t>2022-09-13T07:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -283,7 +283,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t xml:space="preserve">string
+    <t xml:space="preserve">id
 </t>
   </si>
   <si>
@@ -721,6 +721,10 @@
   </si>
   <si>
     <t>Practitioner.qualification.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
   </si>
   <si>
     <t>Unique id for inter-element referencing</t>
@@ -3388,13 +3392,13 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -3445,7 +3449,7 @@
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>78</v>
@@ -3463,7 +3467,7 @@
         <v>77</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>77</v>
@@ -3474,7 +3478,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3503,7 +3507,7 @@
         <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>136</v>
@@ -3556,7 +3560,7 @@
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>78</v>
@@ -3574,7 +3578,7 @@
         <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
@@ -3585,11 +3589,11 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -3611,10 +3615,10 @@
         <v>133</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
         <v>136</v>
@@ -3669,7 +3673,7 @@
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>78</v>
@@ -3698,7 +3702,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -3724,14 +3728,14 @@
         <v>145</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O23" t="s" s="2">
         <v>77</v>
@@ -3780,7 +3784,7 @@
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>78</v>
@@ -3798,7 +3802,7 @@
         <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
@@ -3809,7 +3813,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -3832,13 +3836,13 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -3865,13 +3869,13 @@
         <v>77</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>77</v>
@@ -3889,7 +3893,7 @@
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>87</v>
@@ -3910,7 +3914,7 @@
         <v>222</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -3918,7 +3922,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -3941,17 +3945,17 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>77</v>
@@ -4000,7 +4004,7 @@
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>78</v>
@@ -4018,10 +4022,10 @@
         <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4029,7 +4033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4052,13 +4056,13 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4109,7 +4113,7 @@
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>78</v>
@@ -4127,7 +4131,7 @@
         <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
@@ -4141,7 +4145,7 @@
         <v>214</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>77</v>
@@ -4272,13 +4276,13 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -4329,7 +4333,7 @@
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>78</v>
@@ -4347,7 +4351,7 @@
         <v>77</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
@@ -4358,7 +4362,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4387,7 +4391,7 @@
         <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M29" t="s" s="2">
         <v>136</v>
@@ -4440,7 +4444,7 @@
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>78</v>
@@ -4458,7 +4462,7 @@
         <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>77</v>
@@ -4469,11 +4473,11 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4495,10 +4499,10 @@
         <v>133</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>136</v>
@@ -4553,7 +4557,7 @@
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>78</v>
@@ -4582,7 +4586,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -4605,17 +4609,17 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O31" t="s" s="2">
         <v>77</v>
@@ -4664,7 +4668,7 @@
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>78</v>
@@ -4673,19 +4677,19 @@
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4693,7 +4697,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -4716,13 +4720,13 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4749,11 +4753,11 @@
         <v>77</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="X32" s="2"/>
       <c r="Y32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>77</v>
@@ -4771,7 +4775,7 @@
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>87</v>
@@ -4792,7 +4796,7 @@
         <v>222</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -4800,7 +4804,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -4823,17 +4827,17 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>77</v>
@@ -4882,7 +4886,7 @@
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>78</v>
@@ -4900,10 +4904,10 @@
         <v>77</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -4911,7 +4915,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -4934,13 +4938,13 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -4991,7 +4995,7 @@
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>78</v>
@@ -5009,7 +5013,7 @@
         <v>77</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
@@ -5020,7 +5024,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5043,19 +5047,19 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>77</v>
@@ -5104,7 +5108,7 @@
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>78</v>
@@ -5119,13 +5123,13 @@
         <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$35</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-13T07:22:16+00:00</t>
+    <t>2022-09-17T09:48:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -530,15 +533,7 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  --In general, select the value to be used in the ResourceReference.display based on this:--1. There is more than 1 name-2. Use = usual-3. Period is current to the date of the usage-4. Use = official-5. Other order as decided by internal business rules.</t>
+    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
@@ -1025,6 +1020,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1363,7 +1373,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1472,7 +1482,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1583,7 +1593,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1692,7 +1702,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1803,7 +1813,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -1914,7 +1924,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2025,7 +2035,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2136,7 +2146,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2247,7 +2257,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2360,7 +2370,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2481,13 +2491,13 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2596,13 +2606,13 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -2699,7 +2709,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -2812,7 +2822,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>180</v>
       </c>
@@ -2925,7 +2935,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>189</v>
       </c>
@@ -3036,7 +3046,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>199</v>
       </c>
@@ -3147,7 +3157,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>207</v>
       </c>
@@ -3258,7 +3268,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>214</v>
       </c>
@@ -3367,7 +3377,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>224</v>
       </c>
@@ -3476,7 +3486,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>230</v>
       </c>
@@ -3587,7 +3597,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>233</v>
       </c>
@@ -3700,7 +3710,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>238</v>
       </c>
@@ -3811,7 +3821,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>243</v>
       </c>
@@ -3920,7 +3930,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>251</v>
       </c>
@@ -4031,7 +4041,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>258</v>
       </c>
@@ -4140,7 +4150,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>214</v>
       </c>
@@ -4251,7 +4261,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>224</v>
       </c>
@@ -4360,7 +4370,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>230</v>
       </c>
@@ -4471,7 +4481,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>233</v>
       </c>
@@ -4584,7 +4594,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>238</v>
       </c>
@@ -4695,7 +4705,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>243</v>
       </c>
@@ -4802,7 +4812,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>251</v>
       </c>
@@ -4913,7 +4923,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>258</v>
       </c>
@@ -5022,7 +5032,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>273</v>
       </c>
@@ -5136,6 +5146,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM35">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI34">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$35</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:48:15+00:00</t>
+    <t>2022-09-17T09:59:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitioner</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -533,7 +530,15 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
+    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  ++In general, select the value to be used in the ResourceReference.display based on this:++1. There is more than 1 name+2. Use = usual+3. Period is current to the date of the usage+4. Use = official+5. Other order as decided by internal business rules.</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
@@ -1020,21 +1025,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1373,7 +1363,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1482,7 +1472,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1593,7 +1583,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1702,7 +1692,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1813,7 +1803,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -1924,7 +1914,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2035,7 +2025,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2146,7 +2136,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2257,7 +2247,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2370,7 +2360,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2491,13 +2481,13 @@
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2606,13 +2596,13 @@
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -2709,7 +2699,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -2822,7 +2812,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>180</v>
       </c>
@@ -2935,7 +2925,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>189</v>
       </c>
@@ -3046,7 +3036,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>199</v>
       </c>
@@ -3157,7 +3147,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>207</v>
       </c>
@@ -3268,7 +3258,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>214</v>
       </c>
@@ -3377,7 +3367,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>224</v>
       </c>
@@ -3486,7 +3476,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>230</v>
       </c>
@@ -3597,7 +3587,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>233</v>
       </c>
@@ -3710,7 +3700,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>238</v>
       </c>
@@ -3821,7 +3811,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>243</v>
       </c>
@@ -3930,7 +3920,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>251</v>
       </c>
@@ -4041,7 +4031,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>258</v>
       </c>
@@ -4150,7 +4140,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>214</v>
       </c>
@@ -4261,7 +4251,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>224</v>
       </c>
@@ -4370,7 +4360,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>230</v>
       </c>
@@ -4481,7 +4471,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>233</v>
       </c>
@@ -4594,7 +4584,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>238</v>
       </c>
@@ -4705,7 +4695,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>243</v>
       </c>
@@ -4812,7 +4802,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>251</v>
       </c>
@@ -4923,7 +4913,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>258</v>
       </c>
@@ -5032,7 +5022,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>273</v>
       </c>
@@ -5146,24 +5136,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM35">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:59:31+00:00</t>
+    <t>2022-09-17T10:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T10:02:16+00:00</t>
+    <t>2022-10-04T11:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="282">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T11:09:51+00:00</t>
+    <t>2022-10-04T14:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -850,7 +850,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
+    <t>[DA] Autorisationskode, som specificeret af autorisationsregisteret</t>
   </si>
   <si>
     <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
@@ -867,6 +867,9 @@
   </si>
   <si>
     <t>Identifier</t>
+  </si>
+  <si>
+    <t>[DA] Kode for kvalifikation, som specificeret af autorisationsregisteret</t>
   </si>
   <si>
     <t>extensible</t>
@@ -4723,7 +4726,7 @@
         <v>244</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>246</v>
@@ -4753,11 +4756,11 @@
         <v>77</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X32" s="2"/>
       <c r="Y32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>77</v>
@@ -5024,7 +5027,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5050,16 +5053,16 @@
         <v>244</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>77</v>
@@ -5108,7 +5111,7 @@
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>78</v>
@@ -5123,13 +5126,13 @@
         <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T14:18:04+00:00</t>
+    <t>2022-10-04T19:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T19:52:49+00:00</t>
+    <t>2022-10-04T20:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="281">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T20:54:27+00:00</t>
+    <t>2022-10-11T09:25:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -259,10 +259,6 @@
   </si>
   <si>
     <t>A person who is directly or indirectly involved in the provisioning of healthcare.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -1460,16 +1456,16 @@
         <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AJ2" t="s" s="2">
+      <c r="AK2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AK2" t="s" s="2">
+      <c r="AL2" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>77</v>
@@ -1477,7 +1473,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -1488,28 +1484,28 @@
         <v>78</v>
       </c>
       <c r="F3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
+      <c r="J3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" t="s" s="2">
@@ -1559,13 +1555,13 @@
         <v>77</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AF3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>77</v>
@@ -1588,7 +1584,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -1599,25 +1595,25 @@
         <v>78</v>
       </c>
       <c r="F4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="K4" t="s" s="2">
+      <c r="L4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -1668,19 +1664,19 @@
         <v>77</v>
       </c>
       <c r="AE4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AF4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>77</v>
@@ -1697,7 +1693,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -1708,28 +1704,28 @@
         <v>78</v>
       </c>
       <c r="F5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="K5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="K5" t="s" s="2">
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" t="s" s="2">
@@ -1779,19 +1775,19 @@
         <v>77</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>77</v>
@@ -1808,7 +1804,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -1819,7 +1815,7 @@
         <v>78</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>77</v>
@@ -1831,16 +1827,16 @@
         <v>77</v>
       </c>
       <c r="J6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
@@ -1866,43 +1862,43 @@
         <v>77</v>
       </c>
       <c r="W6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="X6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="X6" t="s" s="2">
+      <c r="Y6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AF6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>77</v>
@@ -1919,18 +1915,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>77</v>
@@ -1942,16 +1938,16 @@
         <v>77</v>
       </c>
       <c r="J7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="K7" t="s" s="2">
+      <c r="L7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
@@ -2001,25 +1997,25 @@
         <v>77</v>
       </c>
       <c r="AE7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>77</v>
@@ -2030,11 +2026,11 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
@@ -2053,16 +2049,16 @@
         <v>77</v>
       </c>
       <c r="J8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="K8" t="s" s="2">
+      <c r="L8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" t="s" s="2">
@@ -2112,7 +2108,7 @@
         <v>77</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AF8" t="s" s="2">
         <v>78</v>
@@ -2130,7 +2126,7 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>77</v>
@@ -2141,11 +2137,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
@@ -2164,16 +2160,16 @@
         <v>77</v>
       </c>
       <c r="J9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="K9" t="s" s="2">
+      <c r="L9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
@@ -2223,7 +2219,7 @@
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>78</v>
@@ -2235,13 +2231,13 @@
         <v>77</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>77</v>
@@ -2252,11 +2248,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
@@ -2269,25 +2265,25 @@
         <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="O10" t="s" s="2">
         <v>77</v>
@@ -2336,7 +2332,7 @@
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>78</v>
@@ -2348,13 +2344,13 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>77</v>
@@ -2365,7 +2361,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2385,20 +2381,20 @@
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="K11" t="s" s="2">
+      <c r="L11" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O11" t="s" s="2">
         <v>77</v>
@@ -2447,7 +2443,7 @@
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>78</v>
@@ -2459,24 +2455,24 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AL11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>152</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2487,111 +2483,111 @@
         <v>78</v>
       </c>
       <c r="F12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="K12" t="s" s="2">
+      <c r="L12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="P12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P12" t="s" s="2">
+      <c r="Q12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="R12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="Q12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK12" t="s" s="2">
+      <c r="AL12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2611,22 +2607,22 @@
         <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="K13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="K13" t="s" s="2">
+      <c r="L13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O13" t="s" s="2">
         <v>77</v>
@@ -2675,7 +2671,7 @@
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>78</v>
@@ -2687,16 +2683,16 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2704,7 +2700,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2724,22 +2720,22 @@
         <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="K14" t="s" s="2">
+      <c r="L14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="O14" t="s" s="2">
         <v>77</v>
@@ -2788,7 +2784,7 @@
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>78</v>
@@ -2800,16 +2796,16 @@
         <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -2817,7 +2813,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2837,22 +2833,22 @@
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="K15" t="s" s="2">
+      <c r="L15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="O15" t="s" s="2">
         <v>77</v>
@@ -2901,7 +2897,7 @@
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>78</v>
@@ -2913,16 +2909,16 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ15" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -2930,7 +2926,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2941,29 +2937,29 @@
         <v>78</v>
       </c>
       <c r="F16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>77</v>
@@ -2988,52 +2984,52 @@
         <v>77</v>
       </c>
       <c r="W16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="X16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="X16" t="s" s="2">
+      <c r="Y16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
+      <c r="AK16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3041,7 +3037,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3052,29 +3048,29 @@
         <v>78</v>
       </c>
       <c r="F17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="K17" t="s" s="2">
+      <c r="L17" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O17" t="s" s="2">
         <v>77</v>
@@ -3123,28 +3119,28 @@
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3152,7 +3148,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3175,17 +3171,17 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="K18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="K18" t="s" s="2">
+      <c r="L18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>77</v>
@@ -3234,7 +3230,7 @@
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>78</v>
@@ -3246,16 +3242,16 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3263,7 +3259,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3286,13 +3282,13 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="K19" t="s" s="2">
+      <c r="L19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -3331,19 +3327,19 @@
         <v>77</v>
       </c>
       <c r="AA19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AB19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AB19" t="s" s="2">
+      <c r="AC19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AC19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="AE19" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>78</v>
@@ -3355,16 +3351,16 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AK19" t="s" s="2">
+      <c r="AL19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3372,7 +3368,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3383,7 +3379,7 @@
         <v>78</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>77</v>
@@ -3395,13 +3391,13 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="K20" t="s" s="2">
+      <c r="L20" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -3452,25 +3448,25 @@
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>77</v>
@@ -3481,11 +3477,11 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -3504,16 +3500,16 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="K21" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="K21" t="s" s="2">
-        <v>134</v>
-      </c>
       <c r="L21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -3563,7 +3559,7 @@
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>78</v>
@@ -3575,13 +3571,13 @@
         <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
@@ -3592,11 +3588,11 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -3609,25 +3605,25 @@
         <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O22" t="s" s="2">
         <v>77</v>
@@ -3676,7 +3672,7 @@
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>78</v>
@@ -3688,13 +3684,13 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
@@ -3705,7 +3701,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -3728,17 +3724,17 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O23" t="s" s="2">
         <v>77</v>
@@ -3787,7 +3783,7 @@
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>78</v>
@@ -3799,13 +3795,13 @@
         <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
@@ -3816,7 +3812,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -3824,10 +3820,10 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>77</v>
@@ -3839,13 +3835,13 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="K24" t="s" s="2">
+      <c r="L24" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -3872,52 +3868,52 @@
         <v>77</v>
       </c>
       <c r="W24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="X24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="X24" t="s" s="2">
+      <c r="Y24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -3925,7 +3921,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -3936,7 +3932,7 @@
         <v>78</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>77</v>
@@ -3948,17 +3944,17 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="K25" t="s" s="2">
+      <c r="L25" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>77</v>
@@ -4007,28 +4003,28 @@
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4036,7 +4032,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4047,7 +4043,7 @@
         <v>78</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>77</v>
@@ -4059,13 +4055,13 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="K26" t="s" s="2">
+      <c r="L26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4116,25 +4112,25 @@
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
@@ -4145,10 +4141,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>77</v>
@@ -4158,7 +4154,7 @@
         <v>78</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>77</v>
@@ -4170,13 +4166,13 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="K27" t="s" s="2">
+      <c r="L27" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4227,7 +4223,7 @@
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>78</v>
@@ -4239,16 +4235,16 @@
         <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4256,7 +4252,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4267,7 +4263,7 @@
         <v>78</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>77</v>
@@ -4279,13 +4275,13 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="K28" t="s" s="2">
+      <c r="L28" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -4336,25 +4332,25 @@
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>77</v>
@@ -4365,11 +4361,11 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4388,16 +4384,16 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="K29" t="s" s="2">
-        <v>134</v>
-      </c>
       <c r="L29" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
@@ -4447,7 +4443,7 @@
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>78</v>
@@ -4459,13 +4455,13 @@
         <v>77</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>77</v>
@@ -4476,11 +4472,11 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4493,25 +4489,25 @@
         <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>77</v>
@@ -4560,7 +4556,7 @@
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>78</v>
@@ -4572,13 +4568,13 @@
         <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
@@ -4589,7 +4585,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -4612,17 +4608,17 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="K31" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="K31" t="s" s="2">
+      <c r="L31" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O31" t="s" s="2">
         <v>77</v>
@@ -4671,7 +4667,7 @@
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>78</v>
@@ -4680,19 +4676,19 @@
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AI31" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
+      <c r="AK31" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4700,7 +4696,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -4708,10 +4704,10 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>77</v>
@@ -4723,13 +4719,13 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4756,11 +4752,11 @@
         <v>77</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="X32" s="2"/>
       <c r="Y32" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>77</v>
@@ -4778,28 +4774,28 @@
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -4807,7 +4803,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -4818,7 +4814,7 @@
         <v>78</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>77</v>
@@ -4830,17 +4826,17 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="K33" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="K33" t="s" s="2">
+      <c r="L33" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>77</v>
@@ -4889,28 +4885,28 @@
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -4918,7 +4914,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -4929,7 +4925,7 @@
         <v>78</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>77</v>
@@ -4941,13 +4937,13 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="K34" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="K34" t="s" s="2">
+      <c r="L34" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -4998,25 +4994,25 @@
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
@@ -5027,7 +5023,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5050,19 +5046,19 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>77</v>
@@ -5087,14 +5083,14 @@
         <v>77</v>
       </c>
       <c r="W35" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="X35" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="X35" t="s" s="2">
+      <c r="Y35" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Y35" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="Z35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5111,7 +5107,7 @@
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>78</v>
@@ -5123,16 +5119,16 @@
         <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ35" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AK35" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AK35" t="s" s="2">
+      <c r="AL35" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-11T09:25:49+00:00</t>
+    <t>2022-10-21T11:28:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:28:25+00:00</t>
+    <t>2022-10-21T11:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:53:19+00:00</t>
+    <t>2022-10-24T14:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="280">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T14:23:47+00:00</t>
+    <t>2022-10-24T22:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>Copyright</t>
-  </si>
-  <si>
-    <t>CC-BY-SA-4.0</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -1140,56 +1137,54 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1245,3893 +1240,3893 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AJ1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>73</v>
       </c>
-      <c r="AK1" t="s" s="1">
+      <c r="AL1" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="AL1" t="s" s="1">
+      <c r="AM1" t="s" s="1">
         <v>75</v>
-      </c>
-      <c r="AM1" t="s" s="1">
-        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F2" t="s" s="2">
+      <c r="G2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="G2" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="L2" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AF2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG2" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AK2" t="s" s="2">
+      <c r="AL2" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AL2" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AM2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
+      <c r="J3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I4" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="J4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="K4" t="s" s="2">
+      <c r="L4" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE4" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AF4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>98</v>
-      </c>
       <c r="AJ4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H5" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="K5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="K5" t="s" s="2">
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="X6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="X6" t="s" s="2">
+      <c r="Y6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="AF6" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="K7" t="s" s="2">
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="AF7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>121</v>
-      </c>
       <c r="AL7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F8" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="K8" t="s" s="2">
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="AF8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>129</v>
-      </c>
       <c r="AL8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F9" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="K9" t="s" s="2">
+      <c r="L9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="AF9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI9" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="AJ9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F10" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F10" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>141</v>
-      </c>
       <c r="O10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG10" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG10" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F11" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F11" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="K11" t="s" s="2">
+      <c r="L11" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG11" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG11" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AL11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="J12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="K12" t="s" s="2">
+      <c r="L12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="P12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="P12" t="s" s="2">
+      <c r="Q12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="R12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Q12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK12" t="s" s="2">
+      <c r="AL12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F13" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="K13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="K13" t="s" s="2">
+      <c r="L13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="O13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG13" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>169</v>
-      </c>
       <c r="AM13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F14" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="K14" t="s" s="2">
+      <c r="L14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="O14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F15" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="K15" t="s" s="2">
+      <c r="L15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N15" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="O15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG15" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL15" t="s" s="2">
-        <v>187</v>
-      </c>
       <c r="AM15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="J16" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="X16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="X16" t="s" s="2">
+      <c r="Y16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
+      <c r="AK16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AL16" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="J17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="K17" t="s" s="2">
+      <c r="L17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>205</v>
-      </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F18" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="K18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="K18" t="s" s="2">
+      <c r="L18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AM18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F19" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J19" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="K19" t="s" s="2">
+      <c r="L19" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AB19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AB19" t="s" s="2">
+      <c r="AC19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AC19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD19" t="s" s="2">
+      <c r="AE19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AE19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
+      <c r="AK19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AK19" t="s" s="2">
+      <c r="AL19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="AM19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="K20" t="s" s="2">
+      <c r="L20" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AF20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>228</v>
-      </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F21" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="K21" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="K21" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="L21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F22" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AF22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F23" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="K24" t="s" s="2">
+      <c r="L24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="X24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="X24" t="s" s="2">
+      <c r="Y24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="K25" t="s" s="2">
+      <c r="L25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="K26" t="s" s="2">
+      <c r="L26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="K27" t="s" s="2">
+      <c r="L27" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J28" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="K28" t="s" s="2">
+      <c r="L28" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AF28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>228</v>
-      </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F29" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J29" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="K29" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="L29" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F30" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>235</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F31" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="K31" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="K31" t="s" s="2">
+      <c r="L31" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AI31" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
+      <c r="AK31" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="X32" s="2"/>
       <c r="Y32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J33" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="K33" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="K33" t="s" s="2">
+      <c r="L33" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="K34" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="K34" t="s" s="2">
+      <c r="L34" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="F35" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="W35" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="X35" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="X35" t="s" s="2">
+      <c r="Y35" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y35" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ35" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AK35" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AK35" t="s" s="2">
+      <c r="AL35" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T22:55:30+00:00</t>
+    <t>2022-11-07T08:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T08:18:22+00:00</t>
+    <t>2022-11-07T15:10:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T15:10:04+00:00</t>
+    <t>2022-11-08T22:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:20:55+00:00</t>
+    <t>2022-11-08T22:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:23:46+00:00</t>
+    <t>2022-11-30T21:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-30T21:48:52+00:00</t>
+    <t>2022-12-01T00:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T00:22:19+00:00</t>
+    <t>2022-12-01T21:15:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T21:15:09+00:00</t>
+    <t>2022-12-05T08:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:13:32+00:00</t>
+    <t>2022-12-05T08:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:52:10+00:00</t>
+    <t>2022-12-05T08:58:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:58:17+00:00</t>
+    <t>2022-12-05T09:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="291">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-24T21:40:58+00:00</t>
+    <t>2023-04-25T17:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -530,18 +533,14 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  --In general, select the value to be used in the ResourceReference.display based on this:--1. There is more than 1 name-2. Use = usual-3. Period is current to the date of the usage-4. Use = official-5. Other order as decided by internal business rules.</t>
+    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ipa-pract-1:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
   </si>
   <si>
     <t>XCN Components</t>
@@ -1052,6 +1051,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1391,7 +1405,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1503,7 +1517,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1617,7 +1631,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1729,7 +1743,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1843,7 +1857,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -1957,7 +1971,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2071,7 +2085,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2185,7 +2199,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2299,7 +2313,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2415,7 +2429,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2529,7 +2543,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -2647,7 +2661,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
@@ -2660,13 +2674,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
@@ -2748,27 +2762,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2791,19 +2805,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2852,7 +2866,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2867,24 +2881,24 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2907,19 +2921,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2968,7 +2982,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2983,24 +2997,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3026,14 +3040,14 @@
         <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3058,13 +3072,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3082,7 +3096,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3097,24 +3111,24 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3137,17 +3151,17 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3196,7 +3210,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3211,24 +3225,24 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3251,17 +3265,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3310,7 +3324,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3328,21 +3342,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3365,13 +3379,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3410,19 +3424,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3437,24 +3451,24 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3477,13 +3491,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3534,7 +3548,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3552,7 +3566,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3561,12 +3575,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3595,7 +3609,7 @@
         <v>134</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>136</v>
@@ -3648,7 +3662,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3666,7 +3680,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3675,16 +3689,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3706,10 +3720,10 @@
         <v>133</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>136</v>
@@ -3764,7 +3778,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3791,12 +3805,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3822,14 +3836,14 @@
         <v>145</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3878,7 +3892,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3896,7 +3910,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3905,12 +3919,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3933,13 +3947,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3966,13 +3980,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -3990,7 +4004,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -4008,21 +4022,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4045,17 +4059,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4104,7 +4118,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4122,21 +4136,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4159,13 +4173,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4216,7 +4230,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4234,7 +4248,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4243,15 +4257,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4273,13 +4287,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4330,7 +4344,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4345,24 +4359,24 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4385,13 +4399,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4442,7 +4456,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4460,7 +4474,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4469,12 +4483,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4503,7 +4517,7 @@
         <v>134</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>136</v>
@@ -4556,7 +4570,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4574,7 +4588,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4583,16 +4597,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4614,10 +4628,10 @@
         <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>136</v>
@@ -4672,7 +4686,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4699,12 +4713,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4727,17 +4741,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4786,7 +4800,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4795,30 +4809,30 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4841,13 +4855,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4874,11 +4888,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4896,7 +4910,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>87</v>
@@ -4914,21 +4928,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4951,17 +4965,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5010,7 +5024,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5028,21 +5042,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5065,13 +5079,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5122,7 +5136,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5140,7 +5154,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5149,12 +5163,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5177,19 +5191,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5238,7 +5252,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5253,19 +5267,37 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN35">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI34">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="290">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-25T17:34:53+00:00</t>
+    <t>2023-04-30T20:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitioner</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -533,14 +530,18 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
+    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  ++In general, select the value to be used in the ResourceReference.display based on this:++1. There is more than 1 name+2. Use = usual+3. Period is current to the date of the usage+4. Use = official+5. Other order as decided by internal business rules.</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ipa-pract-1:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
   </si>
   <si>
     <t>XCN Components</t>
@@ -1051,21 +1052,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1405,7 +1391,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1517,7 +1503,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1631,7 +1617,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1743,7 +1729,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1857,7 +1843,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -1971,7 +1957,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2085,7 +2071,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2199,7 +2185,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2313,7 +2299,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2429,7 +2415,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2543,7 +2529,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -2661,7 +2647,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
@@ -2674,13 +2660,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
@@ -2762,27 +2748,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AN13" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>172</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2805,19 +2791,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2866,7 +2852,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2881,24 +2867,24 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2921,19 +2907,19 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2982,7 +2968,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2997,24 +2983,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AN15" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>190</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3040,14 +3026,14 @@
         <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3072,14 +3058,14 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3096,7 +3082,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3111,24 +3097,24 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
-      <c r="A17" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3151,17 +3137,17 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3210,7 +3196,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3225,24 +3211,24 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AN17" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" hidden="true">
-      <c r="A18" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3265,17 +3251,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3324,7 +3310,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3342,21 +3328,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AN18" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
-      <c r="A19" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3379,13 +3365,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3424,19 +3410,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AC19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AC19" t="s" s="2">
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AD19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>221</v>
-      </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3451,24 +3437,24 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>225</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3491,13 +3477,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3548,7 +3534,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3566,21 +3552,21 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>231</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3609,7 +3595,7 @@
         <v>134</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>136</v>
@@ -3662,7 +3648,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3680,7 +3666,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3689,16 +3675,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3720,10 +3706,10 @@
         <v>133</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>136</v>
@@ -3778,7 +3764,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3805,12 +3791,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3836,14 +3822,14 @@
         <v>145</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3892,7 +3878,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3910,21 +3896,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
-        <v>244</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3947,13 +3933,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3980,14 +3966,14 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>250</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4004,7 +3990,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -4022,21 +4008,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AN24" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4059,17 +4045,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4118,7 +4104,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4136,21 +4122,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>259</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4173,13 +4159,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4230,7 +4216,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4248,24 +4234,24 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
+      <c r="B27" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4287,13 +4273,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4344,7 +4330,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4359,24 +4345,24 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4399,13 +4385,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4456,7 +4442,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4474,21 +4460,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" hidden="true">
-      <c r="A29" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4517,7 +4503,7 @@
         <v>134</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>136</v>
@@ -4570,7 +4556,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4588,7 +4574,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4597,16 +4583,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4628,10 +4614,10 @@
         <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>136</v>
@@ -4686,7 +4672,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4713,12 +4699,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4741,17 +4727,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4800,7 +4786,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4809,30 +4795,30 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
-      <c r="A32" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4855,13 +4841,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4888,11 +4874,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4910,7 +4896,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>87</v>
@@ -4928,21 +4914,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4965,17 +4951,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5024,7 +5010,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5042,21 +5028,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
-      <c r="A34" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5079,13 +5065,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5136,7 +5122,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5154,7 +5140,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5163,12 +5149,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5191,19 +5177,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5252,7 +5238,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5267,37 +5253,19 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN35">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="291">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T00:02:52+00:00</t>
+    <t>2023-11-28T12:13:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,6 +263,10 @@
   </si>
   <si>
     <t>A person who is directly or indirectly involved in the provisioning of healthcare.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -1045,10 +1049,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -1488,16 +1492,16 @@
         <v>77</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>77</v>
@@ -1505,10 +1509,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1519,7 +1523,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -1528,19 +1532,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1590,13 +1594,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1619,10 +1623,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1633,7 +1637,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -1642,16 +1646,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1702,19 +1706,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1731,10 +1735,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1745,28 +1749,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1816,19 +1820,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -1845,10 +1849,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1859,7 +1863,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -1871,16 +1875,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1906,13 +1910,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1930,19 +1934,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -1959,21 +1963,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -1985,16 +1989,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2044,25 +2048,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2073,14 +2077,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2099,16 +2103,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2158,7 +2162,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2176,7 +2180,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2187,14 +2191,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2213,16 +2217,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2272,7 +2276,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2284,13 +2288,13 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2301,14 +2305,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2321,25 +2325,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2388,7 +2392,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2400,13 +2404,13 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2417,10 +2421,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2440,20 +2444,20 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2502,7 +2506,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2514,27 +2518,27 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2545,7 +2549,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2554,105 +2558,105 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="P12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="R12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="R12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2672,22 +2676,22 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2736,7 +2740,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2748,16 +2752,16 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -2765,10 +2769,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2788,22 +2792,22 @@
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2852,7 +2856,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2864,16 +2868,16 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -2881,10 +2885,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2904,22 +2908,22 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2968,7 +2972,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2980,16 +2984,16 @@
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -2997,10 +3001,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3011,7 +3015,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3020,20 +3024,20 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3058,13 +3062,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3082,28 +3086,28 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3111,10 +3115,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3125,7 +3129,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3134,20 +3138,20 @@
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3196,28 +3200,28 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3225,10 +3229,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3251,17 +3255,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3310,7 +3314,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3322,16 +3326,16 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3339,10 +3343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3365,13 +3369,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3410,19 +3414,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3434,16 +3438,16 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3451,10 +3455,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3465,7 +3469,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3477,13 +3481,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3534,13 +3538,13 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
@@ -3552,7 +3556,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3563,14 +3567,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3589,16 +3593,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3648,7 +3652,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3660,13 +3664,13 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3677,14 +3681,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3697,25 +3701,25 @@
         <v>77</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3764,7 +3768,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3776,13 +3780,13 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3793,10 +3797,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3819,17 +3823,17 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3878,7 +3882,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3890,13 +3894,13 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3907,10 +3911,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3918,10 +3922,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -3933,13 +3937,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3966,13 +3970,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -3990,28 +3994,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4019,10 +4023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4033,7 +4037,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4045,17 +4049,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4104,28 +4108,28 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4133,10 +4137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4147,7 +4151,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4159,13 +4163,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4216,25 +4220,25 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4245,13 +4249,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4261,7 +4265,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4273,13 +4277,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4330,7 +4334,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4342,16 +4346,16 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4359,10 +4363,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4373,7 +4377,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4385,13 +4389,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4442,13 +4446,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
@@ -4460,7 +4464,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4471,14 +4475,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4497,16 +4501,16 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4556,7 +4560,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4568,13 +4572,13 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4585,14 +4589,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4605,25 +4609,25 @@
         <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4672,7 +4676,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4684,13 +4688,13 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4701,10 +4705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4727,17 +4731,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4786,7 +4790,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4795,19 +4799,19 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -4815,10 +4819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4826,10 +4830,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -4841,13 +4845,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4874,11 +4878,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4896,28 +4900,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -4925,10 +4929,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4939,7 +4943,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -4951,17 +4955,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5010,28 +5014,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5039,10 +5043,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5053,7 +5057,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5065,13 +5069,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5122,25 +5126,25 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5151,10 +5155,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5177,19 +5181,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5214,13 +5218,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5238,7 +5242,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5250,16 +5254,16 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="292">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -534,18 +537,14 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  --In general, select the value to be used in the ResourceReference.display based on this:--1. There is more than 1 name-2. Use = usual-3. Period is current to the date of the usage-4. Use = official-5. Other order as decided by internal business rules.</t>
+    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ipa-pract-1:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
   </si>
   <si>
     <t>XCN Components</t>
@@ -1056,6 +1055,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1395,7 +1409,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1507,7 +1521,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1621,7 +1635,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1733,7 +1747,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1847,7 +1861,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1961,7 +1975,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2075,7 +2089,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2189,7 +2203,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2303,7 +2317,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2419,7 +2433,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2533,7 +2547,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2651,7 +2665,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2664,13 +2678,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
@@ -2752,27 +2766,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2795,19 +2809,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2856,7 +2870,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2871,24 +2885,24 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2911,19 +2925,19 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2972,7 +2986,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2987,24 +3001,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3030,14 +3044,14 @@
         <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3062,13 +3076,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3086,7 +3100,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3101,24 +3115,24 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3141,17 +3155,17 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3200,7 +3214,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3215,24 +3229,24 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3255,17 +3269,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3314,7 +3328,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3332,21 +3346,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3369,13 +3383,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3414,19 +3428,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3441,24 +3455,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3481,13 +3495,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3538,7 +3552,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3556,7 +3570,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3565,12 +3579,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3599,7 +3613,7 @@
         <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>137</v>
@@ -3652,7 +3666,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3670,7 +3684,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3679,16 +3693,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3710,10 +3724,10 @@
         <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>137</v>
@@ -3768,7 +3782,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3795,12 +3809,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3826,14 +3840,14 @@
         <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3882,7 +3896,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3900,7 +3914,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3909,12 +3923,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3937,13 +3951,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3970,13 +3984,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -3994,7 +4008,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>88</v>
@@ -4012,21 +4026,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4049,17 +4063,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4108,7 +4122,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4126,21 +4140,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4163,13 +4177,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4220,7 +4234,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4238,7 +4252,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4247,15 +4261,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4277,13 +4291,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4334,7 +4348,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4349,24 +4363,24 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4389,13 +4403,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4446,7 +4460,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4464,7 +4478,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4473,12 +4487,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4507,7 +4521,7 @@
         <v>135</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>137</v>
@@ -4560,7 +4574,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4578,7 +4592,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4587,16 +4601,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4618,10 +4632,10 @@
         <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>137</v>
@@ -4676,7 +4690,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4703,12 +4717,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4731,17 +4745,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4790,7 +4804,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4799,30 +4813,30 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4845,13 +4859,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4878,11 +4892,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4900,7 +4914,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -4918,21 +4932,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4955,17 +4969,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5014,7 +5028,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5032,21 +5046,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5069,13 +5083,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5126,7 +5140,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5144,7 +5158,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5153,12 +5167,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5181,19 +5195,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5242,7 +5256,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5257,19 +5271,37 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN35">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI34">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="291">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitioner</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -537,14 +534,18 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
+    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  ++In general, select the value to be used in the ResourceReference.display based on this:++1. There is more than 1 name+2. Use = usual+3. Period is current to the date of the usage+4. Use = official+5. Other order as decided by internal business rules.</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ipa-pract-1:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
   </si>
   <si>
     <t>XCN Components</t>
@@ -1055,21 +1056,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1409,7 +1395,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1521,7 +1507,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1635,7 +1621,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1747,7 +1733,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1861,7 +1847,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1975,7 +1961,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2089,7 +2075,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2203,7 +2189,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2317,7 +2303,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2433,7 +2419,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2547,7 +2533,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2665,7 +2651,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2678,13 +2664,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
@@ -2766,27 +2752,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN13" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2809,19 +2795,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2870,7 +2856,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2885,24 +2871,24 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2925,19 +2911,19 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2986,7 +2972,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3001,24 +2987,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AN15" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3044,14 +3030,14 @@
         <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3076,14 +3062,14 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3100,7 +3086,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3115,24 +3101,24 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
-      <c r="A17" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3155,17 +3141,17 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3214,7 +3200,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3229,24 +3215,24 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AN17" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" hidden="true">
-      <c r="A18" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3269,17 +3255,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3328,7 +3314,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3346,21 +3332,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN18" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
-      <c r="A19" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3383,13 +3369,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3428,19 +3414,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AC19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AC19" t="s" s="2">
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AD19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3455,24 +3441,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3495,13 +3481,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3552,7 +3538,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3570,21 +3556,21 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3613,7 +3599,7 @@
         <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>137</v>
@@ -3666,7 +3652,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3684,7 +3670,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3693,16 +3679,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3724,10 +3710,10 @@
         <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>137</v>
@@ -3782,7 +3768,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3809,12 +3795,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3840,14 +3826,14 @@
         <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3896,7 +3882,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3914,21 +3900,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
-        <v>245</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3951,13 +3937,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3984,14 +3970,14 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4008,7 +3994,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>88</v>
@@ -4026,21 +4012,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AN24" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4063,17 +4049,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4122,7 +4108,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4140,21 +4126,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>260</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4177,13 +4163,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4234,7 +4220,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4252,24 +4238,24 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
+      <c r="B27" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4291,13 +4277,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4348,7 +4334,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4363,24 +4349,24 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4403,13 +4389,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4460,7 +4446,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4478,21 +4464,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" hidden="true">
-      <c r="A29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4521,7 +4507,7 @@
         <v>135</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>137</v>
@@ -4574,7 +4560,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4592,7 +4578,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4601,16 +4587,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4632,10 +4618,10 @@
         <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>137</v>
@@ -4690,7 +4676,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4717,12 +4703,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4745,17 +4731,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4804,7 +4790,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4813,30 +4799,30 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
-      <c r="A32" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4859,13 +4845,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4892,11 +4878,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4914,7 +4900,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -4932,21 +4918,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4969,17 +4955,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5028,7 +5014,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5046,21 +5032,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
-      <c r="A34" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5083,13 +5069,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5140,7 +5126,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5158,7 +5144,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5167,12 +5153,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5195,19 +5181,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5256,7 +5242,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5271,37 +5257,19 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN35">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="292">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -534,18 +537,14 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  --In general, select the value to be used in the ResourceReference.display based on this:--1. There is more than 1 name-2. Use = usual-3. Period is current to the date of the usage-4. Use = official-5. Other order as decided by internal business rules.</t>
+    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ipa-pract-1:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
   </si>
   <si>
     <t>XCN Components</t>
@@ -1056,6 +1055,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1395,7 +1409,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1507,7 +1521,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1621,7 +1635,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1733,7 +1747,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1847,7 +1861,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1961,7 +1975,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2075,7 +2089,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2189,7 +2203,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2303,7 +2317,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2419,7 +2433,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2533,7 +2547,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2651,7 +2665,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2664,13 +2678,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
@@ -2752,27 +2766,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2795,19 +2809,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2856,7 +2870,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2871,24 +2885,24 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2911,19 +2925,19 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2972,7 +2986,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2987,24 +3001,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3030,14 +3044,14 @@
         <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3062,13 +3076,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3086,7 +3100,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3101,24 +3115,24 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3141,17 +3155,17 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3200,7 +3214,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3215,24 +3229,24 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3255,17 +3269,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3314,7 +3328,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3332,21 +3346,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3369,13 +3383,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3414,19 +3428,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3441,24 +3455,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3481,13 +3495,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3538,7 +3552,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3556,7 +3570,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3565,12 +3579,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3599,7 +3613,7 @@
         <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>137</v>
@@ -3652,7 +3666,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3670,7 +3684,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3679,16 +3693,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3710,10 +3724,10 @@
         <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>137</v>
@@ -3768,7 +3782,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3795,12 +3809,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3826,14 +3840,14 @@
         <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3882,7 +3896,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3900,7 +3914,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3909,12 +3923,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3937,13 +3951,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3970,13 +3984,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -3994,7 +4008,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>88</v>
@@ -4012,21 +4026,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4049,17 +4063,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4108,7 +4122,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4126,21 +4140,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4163,13 +4177,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4220,7 +4234,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4238,7 +4252,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4247,15 +4261,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4277,13 +4291,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4334,7 +4348,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4349,24 +4363,24 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4389,13 +4403,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4446,7 +4460,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4464,7 +4478,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4473,12 +4487,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4507,7 +4521,7 @@
         <v>135</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>137</v>
@@ -4560,7 +4574,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4578,7 +4592,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4587,16 +4601,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4618,10 +4632,10 @@
         <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>137</v>
@@ -4676,7 +4690,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4703,12 +4717,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4731,17 +4745,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4790,7 +4804,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4799,30 +4813,30 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4845,13 +4859,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4878,11 +4892,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4900,7 +4914,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -4918,21 +4932,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4955,17 +4969,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5014,7 +5028,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5032,21 +5046,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5069,13 +5083,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5126,7 +5140,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5144,7 +5158,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5153,12 +5167,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5181,19 +5195,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5242,7 +5256,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5257,19 +5271,37 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN35">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI34">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="291">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-practitioner</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -537,14 +534,18 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
+    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  ++In general, select the value to be used in the ResourceReference.display based on this:++1. There is more than 1 name+2. Use = usual+3. Period is current to the date of the usage+4. Use = official+5. Other order as decided by internal business rules.</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ipa-pract-1:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
   </si>
   <si>
     <t>XCN Components</t>
@@ -1055,21 +1056,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1409,7 +1395,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1521,7 +1507,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1635,7 +1621,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1747,7 +1733,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1861,7 +1847,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1975,7 +1961,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2089,7 +2075,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2203,7 +2189,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2317,7 +2303,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2433,7 +2419,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2547,7 +2533,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2665,7 +2651,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2678,13 +2664,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
@@ -2766,27 +2752,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN13" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2809,19 +2795,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2870,7 +2856,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2885,24 +2871,24 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>182</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2925,19 +2911,19 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -2986,7 +2972,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3001,24 +2987,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AN15" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3044,14 +3030,14 @@
         <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3076,14 +3062,14 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3100,7 +3086,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3115,24 +3101,24 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
-      <c r="A17" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3155,17 +3141,17 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3214,7 +3200,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3229,24 +3215,24 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AN17" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" hidden="true">
-      <c r="A18" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3269,17 +3255,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3328,7 +3314,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3346,21 +3332,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN18" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
-      <c r="A19" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3383,13 +3369,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3428,19 +3414,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AC19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AC19" t="s" s="2">
+      <c r="AD19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AD19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3455,24 +3441,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>226</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3495,13 +3481,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3552,7 +3538,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3570,21 +3556,21 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3613,7 +3599,7 @@
         <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>137</v>
@@ -3666,7 +3652,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3684,7 +3670,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3693,16 +3679,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3724,10 +3710,10 @@
         <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>137</v>
@@ -3782,7 +3768,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3809,12 +3795,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3840,14 +3826,14 @@
         <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3896,7 +3882,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3914,21 +3900,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
-        <v>245</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3951,13 +3937,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3984,14 +3970,14 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4008,7 +3994,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>88</v>
@@ -4026,21 +4012,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AN24" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
-      <c r="A25" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4063,17 +4049,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4122,7 +4108,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4140,21 +4126,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>260</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4177,13 +4163,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4234,7 +4220,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4252,24 +4238,24 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
+      <c r="B27" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4291,13 +4277,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4348,7 +4334,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4363,24 +4349,24 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4403,13 +4389,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4460,7 +4446,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4478,21 +4464,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" hidden="true">
-      <c r="A29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4521,7 +4507,7 @@
         <v>135</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>137</v>
@@ -4574,7 +4560,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4592,7 +4578,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4601,16 +4587,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4632,10 +4618,10 @@
         <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>137</v>
@@ -4690,7 +4676,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4717,12 +4703,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4745,17 +4731,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -4804,7 +4790,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4813,30 +4799,30 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
-      <c r="A32" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4859,13 +4845,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4892,11 +4878,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4914,7 +4900,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>88</v>
@@ -4932,21 +4918,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4969,17 +4955,17 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5028,7 +5014,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5046,21 +5032,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
-      <c r="A34" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5083,13 +5069,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5140,7 +5126,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5158,7 +5144,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5167,12 +5153,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5195,19 +5181,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5256,7 +5242,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5271,37 +5257,19 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN35">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-practitioner.xlsx
+++ b/StructureDefinition-dk-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
